--- a/layout/Layout_SWAPS_V10_FILE_SWAP_FLUJO.xlsx
+++ b/layout/Layout_SWAPS_V10_FILE_SWAP_FLUJO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4C91854-AB2F-4302-9599-3E1821AB791A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04EBB93-887E-4757-B1BF-6E153B6F4A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="16440" xr2:uid="{0F5EAD9D-4F05-455F-BC98-C57C32E8ED66}"/>
+    <workbookView xWindow="585" yWindow="945" windowWidth="24720" windowHeight="11310" xr2:uid="{0F5EAD9D-4F05-455F-BC98-C57C32E8ED66}"/>
   </bookViews>
   <sheets>
     <sheet name="FILE_SWAP_FLUJO" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>Catalogo</t>
   </si>
   <si>
-    <t>Comentario BW</t>
-  </si>
-  <si>
     <t>CONT</t>
   </si>
   <si>
@@ -397,6 +394,9 @@
   </si>
   <si>
     <t>Obligatorio</t>
+  </si>
+  <si>
+    <t>Comentarios</t>
   </si>
 </sst>
 </file>
@@ -506,26 +506,6 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -556,6 +536,26 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -604,19 +604,19 @@
       </fill>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="8" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="8" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -656,18 +656,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{21C5D961-4D00-45D6-9A63-B87C03A2849C}" name="Table2457103" displayName="Table2457103" ref="A1:J29" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{21C5D961-4D00-45D6-9A63-B87C03A2849C}" name="Table2457103" displayName="Table2457103" ref="A1:J29" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{08949692-CD4F-4C07-9659-7F77F12F7CC1}" name="Orden" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{3E5FB632-7191-41EB-8FCE-8CA07A9B3E4C}" name="Nombre" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{B5CF7027-5F96-40A6-8601-8F508FAD86C1}" name="Tipo" dataDxfId="6"/>
     <tableColumn id="10" xr3:uid="{9CECDFA1-5DC0-44AF-B4C4-24F542FC5113}" name="Formato"/>
-    <tableColumn id="11" xr3:uid="{932850A8-51E7-41AA-924B-71E8860D9617}" name="Obligatorio" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{200596B1-28C0-427E-B7C3-CCAB8D30A699}" name="Catalogo" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{11A7AD5F-13D6-41A5-8377-A1BACEFAE2BD}" name="Uso" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{49158312-D432-4BDB-98D5-82869C2341BE}" name="Descripcion" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{09768628-CA27-47AE-B370-F36C62964A0A}" name="Validacion" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{8B8F9ACF-BE23-4BBB-A3B6-72CD82951654}" name="Comentario BW" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{932850A8-51E7-41AA-924B-71E8860D9617}" name="Obligatorio" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{200596B1-28C0-427E-B7C3-CCAB8D30A699}" name="Catalogo" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{11A7AD5F-13D6-41A5-8377-A1BACEFAE2BD}" name="Uso" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{49158312-D432-4BDB-98D5-82869C2341BE}" name="Descripcion" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{09768628-CA27-47AE-B370-F36C62964A0A}" name="Validacion" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{8B8F9ACF-BE23-4BBB-A3B6-72CD82951654}" name="Comentarios" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -954,34 +954,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB094581-2BE7-4D9D-BA01-20F2B35C8DBB}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29" customWidth="1"/>
-    <col min="8" max="8" width="60.44140625" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="50.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="19.109375" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" customWidth="1"/>
-    <col min="15" max="15" width="23.44140625" customWidth="1"/>
-    <col min="16" max="16" width="27.33203125" customWidth="1"/>
+    <col min="8" max="8" width="60.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="23.42578125" customWidth="1"/>
+    <col min="16" max="16" width="27.42578125" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" customWidth="1"/>
     <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" customWidth="1"/>
-    <col min="21" max="21" width="11.44140625" customWidth="1"/>
-    <col min="22" max="27" width="8.6640625" customWidth="1"/>
-    <col min="28" max="256" width="9.109375" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" customWidth="1"/>
+    <col min="22" max="27" width="8.5703125" customWidth="1"/>
+    <col min="28" max="256" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -992,10 +992,10 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>6</v>
@@ -1010,792 +1010,792 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" s="10">
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" s="11">
         <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5" s="11">
         <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
         <v>24</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" t="s">
         <v>26</v>
       </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" s="11">
         <v>3</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" t="s">
-        <v>33</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D9" s="10">
         <v>3</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D11" s="10">
         <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="I11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="I13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" s="10">
         <v>3</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15" s="10">
         <v>3</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="I16" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="I17" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" s="10">
         <v>3</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="I18" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="I19" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" s="10">
         <v>20</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="I20" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" s="10">
         <v>1</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="I21" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="I22" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="11">
         <v>3</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="I23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D24" s="11">
         <v>15</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="I24" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D25" s="11">
         <v>15</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="I25" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="I27" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D28" s="11">
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" t="s">
         <v>103</v>
       </c>
-      <c r="G28" t="s">
-        <v>101</v>
-      </c>
-      <c r="H28" t="s">
-        <v>102</v>
-      </c>
-      <c r="I28" t="s">
-        <v>11</v>
-      </c>
-      <c r="J28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
